--- a/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_65005_completo.xlsx
+++ b/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_65005_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7cf8756963524b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8f9d88d22b6044ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,516 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_65005_completo.xlsx
+++ b/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_65005_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8f9d88d22b6044ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdd748ec6fce54c83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,16 +255,2881 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>10:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.9914</x:v>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -275,11 +3140,41 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>06:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.3922</x:v>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +3789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +3804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +3819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +3954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +3969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +4314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +4329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +4344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +4359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +4374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +4389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +4404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +4419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +4434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +4449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +4464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +4479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +4494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +4509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +4524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +4539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +4554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +4569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +4584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +4599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +4614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +4629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +4644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +4659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +4674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +4689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +4704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +4719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +4749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +4764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +4779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +4794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +4809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +4824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +4839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +4854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +4869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +4884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +4899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +4914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +4929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +4944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +4959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +4974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +4989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +5004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +5019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +5034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +5049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +5064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +5079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +5094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +5109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +5124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +5139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +5154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +5169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +5184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +5199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +5214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +5229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +5244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +5259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +5274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +5289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +5304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +5319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +5334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +5364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +5379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +5394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +5424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +5439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +5454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +5469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +5484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +5499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +5514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +5529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +5544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +5559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +5574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +5589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +5604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +5619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +5634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +5649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +5664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +5679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +5694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +5709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +5739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +5754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +5769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +5784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +5799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +5814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +5829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +5844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +5859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +5874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +5889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +5904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +5919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +5934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +5949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +5964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +5979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +5994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +6009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +6024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +6039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3882</x:v>
+        <x:v>     10.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +6054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +6069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +6084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +6099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +6114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +6129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +6144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +6159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +6174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +6189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +6204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +6219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +6234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +6249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +6264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +6279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +6294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +6324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +6339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +6354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +6369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +6384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +6399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +6414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +6429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +6444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +6459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +6474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +6489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +6504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +6519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +6534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +6549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +6564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +6579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3699,7 +6594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3714,7 +6609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3729,7 +6624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3744,7 +6639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,7 +6654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3774,7 +6669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3789,7 +6684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3804,7 +6699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3819,7 +6714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3834,7 +6729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3849,7 +6744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3864,7 +6759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +6774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3894,7 +6789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3909,7 +6804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3924,7 +6819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3939,7 +6834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3954,7 +6849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3969,7 +6864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3984,7 +6879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3999,7 +6894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4014,7 +6909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +6924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4044,7 +6939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4059,7 +6954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4074,7 +6969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +6984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4104,7 +6999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4119,7 +7014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4134,7 +7029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4149,7 +7044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4164,7 +7059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4179,7 +7074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4194,7 +7089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4209,7 +7104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4224,7 +7119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4239,7 +7134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4254,7 +7149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +7164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4284,7 +7179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4299,7 +7194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4314,7 +7209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4329,7 +7224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4344,7 +7239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4359,7 +7254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4374,7 +7269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4389,7 +7284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4404,7 +7299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4419,7 +7314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4434,7 +7329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4449,7 +7344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4464,7 +7359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4479,7 +7374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4494,7 +7389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4509,7 +7404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4524,7 +7419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4539,7 +7434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4554,7 +7449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4569,7 +7464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4584,7 +7479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4599,7 +7494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4614,7 +7509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4629,7 +7524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4644,7 +7539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +7554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4674,7 +7569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4689,7 +7584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4704,7 +7599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4719,7 +7614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4734,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4749,7 +7644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4764,7 +7659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4779,7 +7674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4794,7 +7689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4809,7 +7704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4824,7 +7719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4839,7 +7734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4854,7 +7749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4869,7 +7764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4884,7 +7779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4899,7 +7794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4914,7 +7809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4929,7 +7824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4944,7 +7839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4959,7 +7854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4974,7 +7869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4989,7 +7884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5004,7 +7899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5019,7 +7914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5034,7 +7929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +7944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5064,7 +7959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5079,7 +7974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5094,7 +7989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5109,7 +8004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5124,7 +8019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5139,7 +8034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5154,7 +8049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5169,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5184,7 +8079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5199,7 +8094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5214,7 +8109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +8124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5244,7 +8139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +8154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5274,7 +8169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5289,7 +8184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5304,7 +8199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5319,7 +8214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5334,7 +8229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +8244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5364,7 +8259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5379,7 +8274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5394,7 +8289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +8304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5694,7 +8589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5709,7 +8604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5724,7 +8619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5739,7 +8634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5754,7 +8649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5769,7 +8664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5784,7 +8679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5799,7 +8694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5814,7 +8709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5829,7 +8724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5844,7 +8739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5859,7 +8754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5874,7 +8769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5889,7 +8784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5904,7 +8799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5919,7 +8814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5934,7 +8829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5949,7 +8844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5964,7 +8859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5979,7 +8874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5994,7 +8889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6009,7 +8904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6024,7 +8919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +8934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6054,7 +8949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6069,7 +8964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6084,7 +8979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6099,7 +8994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6114,7 +9009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6129,7 +9024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
